--- a/artfynd/A 24087-2025 artfynd.xlsx
+++ b/artfynd/A 24087-2025 artfynd.xlsx
@@ -813,12 +813,7 @@
         <v>90240058</v>
       </c>
       <c r="B3" t="n">
-        <v>101308</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -850,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>286453.5810243022</v>
+        <v>286454</v>
       </c>
       <c r="R3" t="n">
-        <v>6478688.612926454</v>
+        <v>6478689</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -883,19 +878,9 @@
           <t>2006-06-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2006-06-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 24087-2025 artfynd.xlsx
+++ b/artfynd/A 24087-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>90240058</v>
       </c>
       <c r="B3" t="n">
-        <v>103620</v>
+        <v>103631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24087-2025 artfynd.xlsx
+++ b/artfynd/A 24087-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>90240058</v>
       </c>
       <c r="B3" t="n">
-        <v>103631</v>
+        <v>103639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24087-2025 artfynd.xlsx
+++ b/artfynd/A 24087-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>90240058</v>
       </c>
       <c r="B3" t="n">
-        <v>103639</v>
+        <v>103651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24087-2025 artfynd.xlsx
+++ b/artfynd/A 24087-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>90240058</v>
       </c>
       <c r="B3" t="n">
-        <v>103651</v>
+        <v>103659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24087-2025 artfynd.xlsx
+++ b/artfynd/A 24087-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>90240058</v>
       </c>
       <c r="B3" t="n">
-        <v>103659</v>
+        <v>103661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24087-2025 artfynd.xlsx
+++ b/artfynd/A 24087-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>90240058</v>
       </c>
       <c r="B3" t="n">
-        <v>103661</v>
+        <v>103688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24087-2025 artfynd.xlsx
+++ b/artfynd/A 24087-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>90240058</v>
       </c>
       <c r="B3" t="n">
-        <v>103688</v>
+        <v>103694</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24087-2025 artfynd.xlsx
+++ b/artfynd/A 24087-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>90240058</v>
       </c>
       <c r="B3" t="n">
-        <v>103694</v>
+        <v>103701</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24087-2025 artfynd.xlsx
+++ b/artfynd/A 24087-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>90240058</v>
       </c>
       <c r="B3" t="n">
-        <v>103701</v>
+        <v>103705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24087-2025 artfynd.xlsx
+++ b/artfynd/A 24087-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>90240058</v>
       </c>
       <c r="B3" t="n">
-        <v>103705</v>
+        <v>103712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24087-2025 artfynd.xlsx
+++ b/artfynd/A 24087-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>90240058</v>
       </c>
       <c r="B3" t="n">
-        <v>103715</v>
+        <v>103720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24087-2025 artfynd.xlsx
+++ b/artfynd/A 24087-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>564758</v>
       </c>
       <c r="B2" t="n">
-        <v>101308</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>104232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>286448.574605253</v>
+        <v>286449</v>
       </c>
       <c r="R2" t="n">
-        <v>6478683.633261473</v>
+        <v>6478684</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>OB-Sot-0385</t>
+          <t>Arkiv-OB-Sot-0195</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -762,19 +757,9 @@
           <t>2006-06-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2006-06-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,7 +789,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
@@ -813,7 +798,7 @@
         <v>90240058</v>
       </c>
       <c r="B3" t="n">
-        <v>103720</v>
+        <v>104232</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24087-2025 artfynd.xlsx
+++ b/artfynd/A 24087-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/564758</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,8 +913,17 @@
           <t>Bohusläns Flora 2011</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90240058</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>